--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0001T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.67673367987996</v>
+        <v>6.122469222980493</v>
       </c>
       <c r="D2" t="n">
-        <v>37.06512781540337</v>
+        <v>6.023083270003048</v>
       </c>
       <c r="E2" t="n">
-        <v>12.93093010776309</v>
+        <v>2.101276142511502</v>
       </c>
       <c r="F2" t="n">
-        <v>13.12711820360235</v>
+        <v>2.133156708085383</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.72988916423407</v>
+        <v>5.806106989188037</v>
       </c>
       <c r="D3" t="n">
-        <v>35.08714967429608</v>
+        <v>5.701661822073113</v>
       </c>
       <c r="E3" t="n">
-        <v>12.93093010776309</v>
+        <v>2.101276142511502</v>
       </c>
       <c r="F3" t="n">
-        <v>13.12711820360235</v>
+        <v>2.133156708085383</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>25.88214687561858</v>
+        <v>4.205848867288021</v>
       </c>
       <c r="D4" t="n">
-        <v>26.20635847098647</v>
+        <v>4.258533251535302</v>
       </c>
       <c r="E4" t="n">
-        <v>12.93093010776309</v>
+        <v>2.101276142511502</v>
       </c>
       <c r="F4" t="n">
-        <v>13.12711820360235</v>
+        <v>2.133156708085383</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.11709748209397</v>
+        <v>9.93152834084027</v>
       </c>
       <c r="D5" t="n">
-        <v>61.59331810386622</v>
+        <v>10.00891419187826</v>
       </c>
       <c r="E5" t="n">
-        <v>12.93093010776309</v>
+        <v>2.101276142511502</v>
       </c>
       <c r="F5" t="n">
-        <v>13.12711820360235</v>
+        <v>2.133156708085383</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
